--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04 14:05</t>
+    <t xml:space="preserve">2026-08-07 06:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 06:32</t>
+    <t xml:space="preserve">2026-08-13 12:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-13 12:55</t>
+    <t xml:space="preserve">2026-08-19 12:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:56</t>
+    <t xml:space="preserve">2026-08-28 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:04</t>
+    <t xml:space="preserve">2026-09-01 11:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 11:32</t>
+    <t xml:space="preserve">2026-09-04 20:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 20:07</t>
+    <t xml:space="preserve">2026-09-06 16:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:39</t>
+    <t xml:space="preserve">2026-09-08 11:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
